--- a/public/quote_template.xlsx
+++ b/public/quote_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{748D1447-E4FD-4B14-8776-7FDD9FB2B9DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C1803CB-9740-4825-8B04-128512A17267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9320" yWindow="0" windowWidth="16960" windowHeight="11170" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="문자광고_견적서" sheetId="1" r:id="rId1"/>
@@ -227,59 +227,59 @@
   </si>
   <si>
     <t>발송/지면 유형</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>(인)</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>문시욱</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>기여운</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>010-8478-2564</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>LMS</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>대구 수성구</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>경산</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>금액</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>[경산] 상방공원 호반써밋</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>김정환</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>010-9400-5226</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>30~60대</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>대구 동구</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -661,7 +661,7 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1271,11 +1271,11 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>② "을"은 제1항에서 정한 범위 내에서 성실히 광고를 집행할 의무를 부담하며, 집행 범위의 변경이 필요한 경우 "갑"과 사전 협의하여야 한다.</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1791,11 +1791,11 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>"을"은 본 계약에 따른 광고를 성실히 집행할 의무를 부담하나, 광고 집행 이후의 분양 실적, 고객 유입률, 계약 전환율 등 광고 효과에 대하여는 이를 보증하지 아니한다. "갑"은 광고 효과의 미달을 사유로 계약 해제, 대금 감액 또는 손해배상을 청구할 수 없다.</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -2253,7 +2253,7 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -2635,7 +2635,7 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3074,7 +3074,7 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3456,14 +3456,14 @@
       </rPr>
       <t>.</t>
     </r>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>SKT</t>
   </si>
   <si>
     <t>SKT LMS_경산 상방공원 호반써밋</t>
-    <phoneticPr fontId="20" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3477,104 +3477,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8.5"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Noto Sans CJK SC"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8.5"/>
-      <color rgb="FF1B2A4A"/>
-      <name val="Noto Sans CJK SC"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFC0392B"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFC0392B"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -3633,28 +3535,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF1A1A1A"/>
-      <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
       <sz val="6.5"/>
       <color rgb="FF333333"/>
       <name val="Arial"/>
@@ -3676,6 +3556,128 @@
       <sz val="6.5"/>
       <color rgb="FF333333"/>
       <name val="Noto Sans CJK SC"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="나눔고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8.5"/>
+      <color rgb="FF1B2A4A"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1A1A1A"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC0392B"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFC0392B"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF1B2A4A"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="6.5"/>
+      <color rgb="FF333333"/>
+      <name val="Noto Sans KR"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -3893,87 +3895,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3982,53 +3934,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="22" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="23" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="25" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -4347,943 +4342,956 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <dimension ref="A1:J70"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7265625" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="20.28515625" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.1796875" customWidth="1"/>
+    <col min="7" max="7" width="20.26953125" customWidth="1"/>
+    <col min="8" max="8" width="9.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="7.5" customHeight="1">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:10" ht="7.5" customHeight="1">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="18"/>
-    </row>
-    <row r="2" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="21"/>
-    </row>
-    <row r="3" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A3" s="33" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="21"/>
+    </row>
+    <row r="2" spans="1:10" ht="27.75" customHeight="1">
+      <c r="A2" s="22"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="24"/>
+    </row>
+    <row r="3" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="34" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="27"/>
-    </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1">
-      <c r="A4" s="41" t="s">
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="26"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="1" t="s">
+      <c r="C4" s="31"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="27"/>
-    </row>
-    <row r="5" spans="1:8" ht="18" customHeight="1">
-      <c r="A5" s="42"/>
-      <c r="B5" s="1" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="26"/>
+    </row>
+    <row r="5" spans="1:10" ht="18" customHeight="1">
+      <c r="A5" s="32"/>
+      <c r="B5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="1" t="s">
+      <c r="D5" s="28"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15" t="s">
+      <c r="G5" s="33"/>
+      <c r="H5" s="34" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18" customHeight="1">
-      <c r="A6" s="43"/>
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:10" ht="18" customHeight="1">
+      <c r="A6" s="35"/>
+      <c r="B6" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="2" t="s">
+      <c r="C6" s="31"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="27"/>
-    </row>
-    <row r="7" spans="1:8" ht="18" customHeight="1">
-      <c r="A7" s="41" t="s">
+      <c r="H6" s="26"/>
+    </row>
+    <row r="7" spans="1:10" ht="18" customHeight="1">
+      <c r="A7" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="1" t="s">
+      <c r="D7" s="28"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="27"/>
-    </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1">
-      <c r="A8" s="42"/>
-      <c r="B8" s="1" t="s">
+      <c r="H7" s="26"/>
+    </row>
+    <row r="8" spans="1:10" ht="18" customHeight="1">
+      <c r="A8" s="32"/>
+      <c r="B8" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="1" t="s">
+      <c r="D8" s="28"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="34" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1">
-      <c r="A9" s="42"/>
-      <c r="B9" s="1" t="s">
+    <row r="9" spans="1:10" ht="18" customHeight="1">
+      <c r="A9" s="32"/>
+      <c r="B9" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="2" t="s">
+      <c r="D9" s="28"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="27"/>
-    </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1">
-      <c r="A10" s="43"/>
-      <c r="B10" s="2" t="s">
+      <c r="H9" s="26"/>
+    </row>
+    <row r="10" spans="1:10" ht="18" customHeight="1">
+      <c r="A10" s="35"/>
+      <c r="B10" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="1" t="s">
+      <c r="D10" s="28"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="45">
+      <c r="G10" s="38">
         <v>46121</v>
       </c>
-      <c r="H10" s="27"/>
-    </row>
-    <row r="11" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A11" s="4" t="s">
+      <c r="H10" s="26"/>
+    </row>
+    <row r="11" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A11" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="4" t="str">
+      <c r="E11" s="39" t="str">
         <f>IF(OR(B12="호갱노노_단지마커",B12="직방_단지마커",B12="프리미엄_비즈마커"),"기간(일)","발송수량")</f>
         <v>발송수량</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="50" t="s">
+      <c r="G11" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="H11" s="27"/>
-    </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1">
-      <c r="A12" s="5">
+      <c r="H11" s="26"/>
+      <c r="J11" s="18"/>
+    </row>
+    <row r="12" spans="1:10" ht="18" customHeight="1">
+      <c r="A12" s="41">
         <v>1</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="43">
         <v>100000</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="43">
         <v>100</v>
       </c>
-      <c r="G12" s="53">
+      <c r="G12" s="44">
         <f>IF(OR(F12="",E12=""),0,E12*F12)</f>
         <v>10000000</v>
       </c>
-      <c r="H12" s="27"/>
-    </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1">
-      <c r="A13" s="47" t="s">
+      <c r="H12" s="26"/>
+    </row>
+    <row r="13" spans="1:10" ht="18" customHeight="1">
+      <c r="A13" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="8" t="s">
+      <c r="D13" s="26"/>
+      <c r="E13" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="26"/>
-      <c r="H13" s="27"/>
-    </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1">
-      <c r="A14" s="42"/>
-      <c r="B14" s="8" t="s">
+      <c r="G13" s="28"/>
+      <c r="H13" s="26"/>
+    </row>
+    <row r="14" spans="1:10" ht="18" customHeight="1">
+      <c r="A14" s="32"/>
+      <c r="B14" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="27"/>
-    </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1">
-      <c r="A15" s="42"/>
-      <c r="B15" s="8" t="s">
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="26"/>
+    </row>
+    <row r="15" spans="1:10" ht="18" customHeight="1">
+      <c r="A15" s="32"/>
+      <c r="B15" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="27"/>
-    </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1">
-      <c r="A16" s="43"/>
-      <c r="B16" s="8" t="s">
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="26"/>
+    </row>
+    <row r="16" spans="1:10" ht="18" customHeight="1">
+      <c r="A16" s="35"/>
+      <c r="B16" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="27"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="26"/>
     </row>
     <row r="17" spans="1:8" ht="24" customHeight="1">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="27"/>
-      <c r="C17" s="38" t="s">
+      <c r="B17" s="26"/>
+      <c r="C17" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="27"/>
-      <c r="F17" s="9" t="s">
+      <c r="D17" s="28"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="50">
         <f>G12*1.1</f>
         <v>11000000</v>
       </c>
-      <c r="H17" s="27"/>
+      <c r="H17" s="26"/>
     </row>
     <row r="18" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A18" s="32" t="s">
+      <c r="A18" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="26"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="27"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="26"/>
     </row>
     <row r="19" spans="1:8" ht="12" customHeight="1">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="18"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="21"/>
     </row>
     <row r="20" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A20" s="39" t="s">
+      <c r="A20" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="24"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="55"/>
     </row>
     <row r="21" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="24"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="55"/>
     </row>
     <row r="22" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="24"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="55"/>
     </row>
     <row r="23" spans="1:8" ht="1.5" customHeight="1">
-      <c r="A23" s="10"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="11"/>
-      <c r="H23" s="12"/>
+      <c r="A23" s="1"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8" ht="12" customHeight="1">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="24"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8" ht="11.25" customHeight="1">
-      <c r="A25" s="52" t="s">
+      <c r="A25" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="24"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8" ht="1.5" customHeight="1">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="12"/>
+      <c r="A26" s="1"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="3"/>
     </row>
     <row r="27" spans="1:8" ht="12" customHeight="1">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="24"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="6"/>
     </row>
     <row r="28" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="24"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+      <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8" ht="3" customHeight="1">
-      <c r="A29" s="54" t="s">
+      <c r="A29" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="24"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+      <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8" ht="1.5" customHeight="1">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="12"/>
+      <c r="A30" s="1"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:8" ht="12" customHeight="1">
-      <c r="A31" s="22" t="s">
+      <c r="A31" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="24"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="24"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="24"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8" ht="1.5" customHeight="1">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="12"/>
+      <c r="A34" s="1"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="3"/>
     </row>
     <row r="35" spans="1:8" ht="12" customHeight="1">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="24"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-      <c r="H36" s="24"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A37" s="29" t="s">
+      <c r="A37" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
-      <c r="H37" s="24"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="23"/>
-      <c r="H38" s="24"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="23"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="23"/>
-      <c r="H39" s="24"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8" ht="1.5" customHeight="1">
-      <c r="A40" s="10"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="12"/>
+      <c r="A40" s="1"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="3"/>
     </row>
     <row r="41" spans="1:8" ht="12" customHeight="1">
-      <c r="A41" s="22" t="s">
+      <c r="A41" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="23"/>
-      <c r="H41" s="24"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8" ht="23.25" customHeight="1">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="24"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" ht="1.5" customHeight="1">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="12"/>
+      <c r="A43" s="1"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="3"/>
     </row>
     <row r="44" spans="1:8" ht="12" customHeight="1">
-      <c r="A44" s="22" t="s">
+      <c r="A44" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="24"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="6"/>
     </row>
     <row r="45" spans="1:8" ht="18.75" customHeight="1">
-      <c r="A45" s="29" t="s">
+      <c r="A45" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="23"/>
-      <c r="H45" s="24"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="6"/>
     </row>
     <row r="46" spans="1:8" ht="1.5" customHeight="1">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="12"/>
+      <c r="A46" s="1"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="3"/>
     </row>
     <row r="47" spans="1:8" ht="12" customHeight="1">
-      <c r="A47" s="22" t="s">
+      <c r="A47" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="23"/>
-      <c r="H47" s="24"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="6"/>
     </row>
     <row r="48" spans="1:8" ht="11.25" customHeight="1">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="23"/>
-      <c r="H48" s="24"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="6"/>
     </row>
     <row r="49" spans="1:8" ht="12.75" customHeight="1">
-      <c r="A49" s="30" t="s">
+      <c r="A49" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="24"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="6"/>
     </row>
     <row r="50" spans="1:8" ht="1.5" hidden="1" customHeight="1">
-      <c r="A50" s="10"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="11"/>
-      <c r="E50" s="11"/>
-      <c r="F50" s="11"/>
-      <c r="G50" s="11"/>
-      <c r="H50" s="12"/>
+      <c r="A50" s="1"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="3"/>
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1">
-      <c r="A51" s="22" t="s">
+      <c r="A51" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="23"/>
-      <c r="H51" s="24"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="6"/>
     </row>
     <row r="52" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A52" s="30" t="s">
+      <c r="A52" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="24"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="6"/>
     </row>
     <row r="53" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A53" s="30" t="s">
+      <c r="A53" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
-      <c r="D53" s="23"/>
-      <c r="E53" s="23"/>
-      <c r="F53" s="23"/>
-      <c r="G53" s="23"/>
-      <c r="H53" s="24"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="6"/>
     </row>
     <row r="54" spans="1:8" ht="1.5" customHeight="1">
-      <c r="A54" s="10"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
-      <c r="D54" s="11"/>
-      <c r="E54" s="11"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="11"/>
-      <c r="H54" s="12"/>
+      <c r="A54" s="1"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="H54" s="3"/>
     </row>
     <row r="55" spans="1:8" ht="12" customHeight="1">
-      <c r="A55" s="22" t="s">
+      <c r="A55" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="24"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="6"/>
     </row>
     <row r="56" spans="1:8" ht="23.25" customHeight="1">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23"/>
-      <c r="E56" s="23"/>
-      <c r="F56" s="23"/>
-      <c r="G56" s="23"/>
-      <c r="H56" s="24"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="6"/>
     </row>
     <row r="57" spans="1:8" ht="0.75" customHeight="1">
-      <c r="A57" s="10"/>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="12"/>
+      <c r="A57" s="1"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="3"/>
     </row>
     <row r="58" spans="1:8" ht="12" customHeight="1">
-      <c r="A58" s="22" t="s">
+      <c r="A58" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
-      <c r="D58" s="23"/>
-      <c r="E58" s="23"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="23"/>
-      <c r="H58" s="24"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="6"/>
     </row>
     <row r="59" spans="1:8" ht="19.5" customHeight="1">
-      <c r="A59" s="39" t="s">
+      <c r="A59" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="23"/>
-      <c r="E59" s="23"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="23"/>
-      <c r="H59" s="24"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="6"/>
     </row>
     <row r="60" spans="1:8" ht="1.5" customHeight="1">
-      <c r="A60" s="10"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
-      <c r="H60" s="12"/>
+      <c r="A60" s="1"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="3"/>
     </row>
     <row r="61" spans="1:8" ht="12" customHeight="1">
-      <c r="A61" s="22" t="s">
+      <c r="A61" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B61" s="23"/>
-      <c r="C61" s="23"/>
-      <c r="D61" s="23"/>
-      <c r="E61" s="23"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="23"/>
-      <c r="H61" s="24"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="6"/>
     </row>
     <row r="62" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A62" s="29" t="s">
+      <c r="A62" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B62" s="23"/>
-      <c r="C62" s="23"/>
-      <c r="D62" s="23"/>
-      <c r="E62" s="23"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="23"/>
-      <c r="H62" s="24"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="6"/>
     </row>
     <row r="63" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A63" s="29" t="s">
+      <c r="A63" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B63" s="23"/>
-      <c r="C63" s="23"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="23"/>
-      <c r="F63" s="23"/>
-      <c r="G63" s="23"/>
-      <c r="H63" s="24"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="6"/>
     </row>
     <row r="64" spans="1:8" ht="10.5" customHeight="1">
-      <c r="A64" s="29" t="s">
+      <c r="A64" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B64" s="23"/>
-      <c r="C64" s="23"/>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="24"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="6"/>
     </row>
     <row r="65" spans="1:8" ht="1.5" customHeight="1">
-      <c r="A65" s="10"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="12"/>
+      <c r="A65" s="1"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+      <c r="H65" s="3"/>
     </row>
     <row r="66" spans="1:8" ht="12" customHeight="1">
-      <c r="A66" s="22" t="s">
+      <c r="A66" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B66" s="23"/>
-      <c r="C66" s="23"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="23"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="23"/>
-      <c r="H66" s="24"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="6"/>
     </row>
     <row r="67" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A67" s="39" t="s">
+      <c r="A67" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B67" s="23"/>
-      <c r="C67" s="23"/>
-      <c r="D67" s="23"/>
-      <c r="E67" s="23"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="23"/>
-      <c r="H67" s="24"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="6"/>
     </row>
     <row r="68" spans="1:8" ht="1.5" customHeight="1">
-      <c r="A68" s="10"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="11"/>
-      <c r="D68" s="11"/>
-      <c r="E68" s="11"/>
-      <c r="F68" s="11"/>
-      <c r="G68" s="11"/>
-      <c r="H68" s="12"/>
+      <c r="A68" s="1"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="3"/>
     </row>
     <row r="69" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A69" s="40" t="s">
+      <c r="A69" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="27"/>
+      <c r="B69" s="7"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="7"/>
+      <c r="H69" s="8"/>
     </row>
     <row r="70" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A70" s="35" t="s">
+      <c r="A70" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="36"/>
-      <c r="C70" s="36"/>
-      <c r="D70" s="36"/>
-      <c r="E70" s="36"/>
-      <c r="F70" s="36"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="37"/>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
+      <c r="G70" s="16"/>
+      <c r="H70" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A69:H69"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A7:A10"/>
@@ -5300,40 +5308,28 @@
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A63:H63"/>
   </mergeCells>
-  <phoneticPr fontId="20" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"호갱노노_단지마커,직방_단지마커,프리미엄_비즈마커,호갱노노_채널톡,직방_채널톡,SKT,KT,신한카드,롯데카드,국민카드,BC카드,L포인트"</formula1>

--- a/public/quote_template.xlsx
+++ b/public/quote_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB72EFE3-CA3F-4B8D-B605-337144FE7FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C07DDE-038E-44A9-A349-1145657E3A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -329,7 +329,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -454,46 +454,46 @@
       <b/>
       <sz val="7"/>
       <color rgb="FF1B2A4A"/>
-      <name val="NanumGothic"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="NanumGothic"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="6.5"/>
       <color rgb="FF333333"/>
-      <name val="NanumGothic"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="NanumGothic"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
-      <name val="NanumGothic"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="NanumGothic"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
     <font>
       <b/>
       <sz val="7"/>
       <color theme="1"/>
-      <name val="NanumGothic"/>
+      <name val="Noto Sans KR"/>
+      <family val="3"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -710,7 +710,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -797,34 +797,30 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1463,603 +1459,603 @@
       <c r="G18" s="11"/>
       <c r="H18" s="9"/>
     </row>
-    <row r="19" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
-    </row>
-    <row r="20" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="38" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
-      <c r="H20" s="40"/>
-    </row>
-    <row r="21" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="38" t="s">
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="38"/>
+    </row>
+    <row r="21" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
-      <c r="H21" s="40"/>
-    </row>
-    <row r="22" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="38" t="s">
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="38"/>
+    </row>
+    <row r="22" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="40"/>
-    </row>
-    <row r="23" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="41"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="43"/>
-    </row>
-    <row r="24" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="44" t="s">
+      <c r="B22" s="37"/>
+      <c r="C22" s="37"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="38"/>
+    </row>
+    <row r="23" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="39"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="40"/>
+      <c r="H23" s="41"/>
+    </row>
+    <row r="24" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="40"/>
-    </row>
-    <row r="25" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="38" t="s">
+      <c r="B24" s="37"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="37"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="38"/>
+    </row>
+    <row r="25" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
-      <c r="H25" s="40"/>
-    </row>
-    <row r="26" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="41"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="43"/>
-    </row>
-    <row r="27" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="44" t="s">
+      <c r="B25" s="37"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="38"/>
+    </row>
+    <row r="26" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="39"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="40"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="41"/>
+    </row>
+    <row r="27" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-      <c r="H27" s="40"/>
-    </row>
-    <row r="28" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="38" t="s">
+      <c r="B27" s="37"/>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="38"/>
+    </row>
+    <row r="28" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
-      <c r="H28" s="40"/>
-    </row>
-    <row r="29" spans="1:8" ht="3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="45" t="s">
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="38"/>
+    </row>
+    <row r="29" spans="1:8" ht="3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
-      <c r="H29" s="40"/>
-    </row>
-    <row r="30" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="41"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="43"/>
-    </row>
-    <row r="31" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="44" t="s">
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="38"/>
+    </row>
+    <row r="30" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="39"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="40"/>
+      <c r="G30" s="40"/>
+      <c r="H30" s="41"/>
+    </row>
+    <row r="31" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="42" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="40"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="38" t="s">
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="38"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="40"/>
-    </row>
-    <row r="33" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="38" t="s">
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="38"/>
+    </row>
+    <row r="33" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="40"/>
-    </row>
-    <row r="34" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="41"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="43"/>
-    </row>
-    <row r="35" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="44" t="s">
+      <c r="B33" s="37"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="38"/>
+    </row>
+    <row r="34" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="39"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="40"/>
+      <c r="G34" s="40"/>
+      <c r="H34" s="41"/>
+    </row>
+    <row r="35" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="39"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="40"/>
-    </row>
-    <row r="36" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="38" t="s">
+      <c r="B35" s="37"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="38"/>
+    </row>
+    <row r="36" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="39"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="40"/>
-    </row>
-    <row r="37" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="38" t="s">
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="38"/>
+    </row>
+    <row r="37" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="39"/>
-      <c r="C37" s="39"/>
-      <c r="D37" s="39"/>
-      <c r="E37" s="39"/>
-      <c r="F37" s="39"/>
-      <c r="G37" s="39"/>
-      <c r="H37" s="40"/>
-    </row>
-    <row r="38" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="38" t="s">
+      <c r="B37" s="37"/>
+      <c r="C37" s="37"/>
+      <c r="D37" s="37"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
+      <c r="G37" s="37"/>
+      <c r="H37" s="38"/>
+    </row>
+    <row r="38" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="36" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="39"/>
-      <c r="C38" s="39"/>
-      <c r="D38" s="39"/>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="39"/>
-      <c r="H38" s="40"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="38" t="s">
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="38"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="39"/>
-      <c r="C39" s="39"/>
-      <c r="D39" s="39"/>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="39"/>
-      <c r="H39" s="40"/>
-    </row>
-    <row r="40" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="41"/>
-      <c r="B40" s="42"/>
-      <c r="C40" s="42"/>
-      <c r="D40" s="42"/>
-      <c r="E40" s="42"/>
-      <c r="F40" s="42"/>
-      <c r="G40" s="42"/>
-      <c r="H40" s="43"/>
-    </row>
-    <row r="41" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="44" t="s">
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37"/>
+      <c r="H39" s="38"/>
+    </row>
+    <row r="40" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="39"/>
+      <c r="B40" s="40"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="40"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="41"/>
+    </row>
+    <row r="41" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="39"/>
-      <c r="C41" s="39"/>
-      <c r="D41" s="39"/>
-      <c r="E41" s="39"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="39"/>
-      <c r="H41" s="40"/>
-    </row>
-    <row r="42" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="38" t="s">
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="38"/>
+    </row>
+    <row r="42" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="39"/>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="39"/>
-      <c r="H42" s="40"/>
-    </row>
-    <row r="43" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="41"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="42"/>
-      <c r="D43" s="42"/>
-      <c r="E43" s="42"/>
-      <c r="F43" s="42"/>
-      <c r="G43" s="42"/>
-      <c r="H43" s="43"/>
-    </row>
-    <row r="44" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="44" t="s">
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="38"/>
+    </row>
+    <row r="43" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="39"/>
+      <c r="B43" s="40"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="41"/>
+    </row>
+    <row r="44" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="39"/>
-      <c r="C44" s="39"/>
-      <c r="D44" s="39"/>
-      <c r="E44" s="39"/>
-      <c r="F44" s="39"/>
-      <c r="G44" s="39"/>
-      <c r="H44" s="40"/>
-    </row>
-    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="38" t="s">
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="38"/>
+    </row>
+    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="B45" s="39"/>
-      <c r="C45" s="39"/>
-      <c r="D45" s="39"/>
-      <c r="E45" s="39"/>
-      <c r="F45" s="39"/>
-      <c r="G45" s="39"/>
-      <c r="H45" s="40"/>
-    </row>
-    <row r="46" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="41"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="42"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="42"/>
-      <c r="H46" s="43"/>
-    </row>
-    <row r="47" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="44" t="s">
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37"/>
+      <c r="H45" s="38"/>
+    </row>
+    <row r="46" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="39"/>
+      <c r="B46" s="40"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="40"/>
+      <c r="E46" s="40"/>
+      <c r="F46" s="40"/>
+      <c r="G46" s="40"/>
+      <c r="H46" s="41"/>
+    </row>
+    <row r="47" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="39"/>
-      <c r="C47" s="39"/>
-      <c r="D47" s="39"/>
-      <c r="E47" s="39"/>
-      <c r="F47" s="39"/>
-      <c r="G47" s="39"/>
-      <c r="H47" s="40"/>
-    </row>
-    <row r="48" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="38" t="s">
+      <c r="B47" s="37"/>
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37"/>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="38"/>
+    </row>
+    <row r="48" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="B48" s="39"/>
-      <c r="C48" s="39"/>
-      <c r="D48" s="39"/>
-      <c r="E48" s="39"/>
-      <c r="F48" s="39"/>
-      <c r="G48" s="39"/>
-      <c r="H48" s="40"/>
-    </row>
-    <row r="49" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="38" t="s">
+      <c r="B48" s="37"/>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="F48" s="37"/>
+      <c r="G48" s="37"/>
+      <c r="H48" s="38"/>
+    </row>
+    <row r="49" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="B49" s="39"/>
-      <c r="C49" s="39"/>
-      <c r="D49" s="39"/>
-      <c r="E49" s="39"/>
-      <c r="F49" s="39"/>
-      <c r="G49" s="39"/>
-      <c r="H49" s="40"/>
-    </row>
-    <row r="50" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="41"/>
-      <c r="B50" s="42"/>
-      <c r="C50" s="42"/>
-      <c r="D50" s="42"/>
-      <c r="E50" s="42"/>
-      <c r="F50" s="42"/>
-      <c r="G50" s="42"/>
-      <c r="H50" s="43"/>
-    </row>
-    <row r="51" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="44" t="s">
+      <c r="B49" s="37"/>
+      <c r="C49" s="37"/>
+      <c r="D49" s="37"/>
+      <c r="E49" s="37"/>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37"/>
+      <c r="H49" s="38"/>
+    </row>
+    <row r="50" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="39"/>
+      <c r="B50" s="40"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="40"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="40"/>
+      <c r="H50" s="41"/>
+    </row>
+    <row r="51" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="B51" s="39"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="39"/>
-      <c r="E51" s="39"/>
-      <c r="F51" s="39"/>
-      <c r="G51" s="39"/>
-      <c r="H51" s="40"/>
-    </row>
-    <row r="52" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="38" t="s">
+      <c r="B51" s="37"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="38"/>
+    </row>
+    <row r="52" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="B52" s="39"/>
-      <c r="C52" s="39"/>
-      <c r="D52" s="39"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39"/>
-      <c r="G52" s="39"/>
-      <c r="H52" s="40"/>
-    </row>
-    <row r="53" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="38" t="s">
+      <c r="B52" s="37"/>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37"/>
+      <c r="H52" s="38"/>
+    </row>
+    <row r="53" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="B53" s="39"/>
-      <c r="C53" s="39"/>
-      <c r="D53" s="39"/>
-      <c r="E53" s="39"/>
-      <c r="F53" s="39"/>
-      <c r="G53" s="39"/>
-      <c r="H53" s="40"/>
-    </row>
-    <row r="54" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="41"/>
-      <c r="B54" s="42"/>
-      <c r="C54" s="42"/>
-      <c r="D54" s="42"/>
-      <c r="E54" s="42"/>
-      <c r="F54" s="42"/>
-      <c r="G54" s="42"/>
-      <c r="H54" s="43"/>
-    </row>
-    <row r="55" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="44" t="s">
+      <c r="B53" s="37"/>
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37"/>
+      <c r="G53" s="37"/>
+      <c r="H53" s="38"/>
+    </row>
+    <row r="54" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="39"/>
+      <c r="B54" s="40"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="40"/>
+      <c r="E54" s="40"/>
+      <c r="F54" s="40"/>
+      <c r="G54" s="40"/>
+      <c r="H54" s="41"/>
+    </row>
+    <row r="55" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="B55" s="39"/>
-      <c r="C55" s="39"/>
-      <c r="D55" s="39"/>
-      <c r="E55" s="39"/>
-      <c r="F55" s="39"/>
-      <c r="G55" s="39"/>
-      <c r="H55" s="40"/>
-    </row>
-    <row r="56" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="38" t="s">
+      <c r="B55" s="37"/>
+      <c r="C55" s="37"/>
+      <c r="D55" s="37"/>
+      <c r="E55" s="37"/>
+      <c r="F55" s="37"/>
+      <c r="G55" s="37"/>
+      <c r="H55" s="38"/>
+    </row>
+    <row r="56" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="B56" s="39"/>
-      <c r="C56" s="39"/>
-      <c r="D56" s="39"/>
-      <c r="E56" s="39"/>
-      <c r="F56" s="39"/>
-      <c r="G56" s="39"/>
-      <c r="H56" s="40"/>
-    </row>
-    <row r="57" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="41"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="42"/>
-      <c r="D57" s="42"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="43"/>
-    </row>
-    <row r="58" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="44" t="s">
+      <c r="B56" s="37"/>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
+      <c r="H56" s="38"/>
+    </row>
+    <row r="57" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="39"/>
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="41"/>
+    </row>
+    <row r="58" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="39"/>
-      <c r="C58" s="39"/>
-      <c r="D58" s="39"/>
-      <c r="E58" s="39"/>
-      <c r="F58" s="39"/>
-      <c r="G58" s="39"/>
-      <c r="H58" s="40"/>
-    </row>
-    <row r="59" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="38" t="s">
+      <c r="B58" s="37"/>
+      <c r="C58" s="37"/>
+      <c r="D58" s="37"/>
+      <c r="E58" s="37"/>
+      <c r="F58" s="37"/>
+      <c r="G58" s="37"/>
+      <c r="H58" s="38"/>
+    </row>
+    <row r="59" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="36" t="s">
         <v>52</v>
       </c>
-      <c r="B59" s="39"/>
-      <c r="C59" s="39"/>
-      <c r="D59" s="39"/>
-      <c r="E59" s="39"/>
-      <c r="F59" s="39"/>
-      <c r="G59" s="39"/>
-      <c r="H59" s="40"/>
-    </row>
-    <row r="60" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="41"/>
-      <c r="B60" s="42"/>
-      <c r="C60" s="42"/>
-      <c r="D60" s="42"/>
-      <c r="E60" s="42"/>
-      <c r="F60" s="42"/>
-      <c r="G60" s="42"/>
-      <c r="H60" s="43"/>
-    </row>
-    <row r="61" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="44" t="s">
+      <c r="B59" s="37"/>
+      <c r="C59" s="37"/>
+      <c r="D59" s="37"/>
+      <c r="E59" s="37"/>
+      <c r="F59" s="37"/>
+      <c r="G59" s="37"/>
+      <c r="H59" s="38"/>
+    </row>
+    <row r="60" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="39"/>
+      <c r="B60" s="40"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="40"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="40"/>
+      <c r="G60" s="40"/>
+      <c r="H60" s="41"/>
+    </row>
+    <row r="61" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="B61" s="39"/>
-      <c r="C61" s="39"/>
-      <c r="D61" s="39"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="39"/>
-      <c r="H61" s="40"/>
-    </row>
-    <row r="62" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="38" t="s">
+      <c r="B61" s="37"/>
+      <c r="C61" s="37"/>
+      <c r="D61" s="37"/>
+      <c r="E61" s="37"/>
+      <c r="F61" s="37"/>
+      <c r="G61" s="37"/>
+      <c r="H61" s="38"/>
+    </row>
+    <row r="62" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="B62" s="39"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="39"/>
-      <c r="E62" s="39"/>
-      <c r="F62" s="39"/>
-      <c r="G62" s="39"/>
-      <c r="H62" s="40"/>
-    </row>
-    <row r="63" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="38" t="s">
+      <c r="B62" s="37"/>
+      <c r="C62" s="37"/>
+      <c r="D62" s="37"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
+      <c r="H62" s="38"/>
+    </row>
+    <row r="63" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B63" s="39"/>
-      <c r="C63" s="39"/>
-      <c r="D63" s="39"/>
-      <c r="E63" s="39"/>
-      <c r="F63" s="39"/>
-      <c r="G63" s="39"/>
-      <c r="H63" s="40"/>
-    </row>
-    <row r="64" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="38" t="s">
+      <c r="B63" s="37"/>
+      <c r="C63" s="37"/>
+      <c r="D63" s="37"/>
+      <c r="E63" s="37"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
+      <c r="H63" s="38"/>
+    </row>
+    <row r="64" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="B64" s="39"/>
-      <c r="C64" s="39"/>
-      <c r="D64" s="39"/>
-      <c r="E64" s="39"/>
-      <c r="F64" s="39"/>
-      <c r="G64" s="39"/>
-      <c r="H64" s="40"/>
-    </row>
-    <row r="65" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="41"/>
-      <c r="B65" s="42"/>
-      <c r="C65" s="42"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="42"/>
-      <c r="F65" s="42"/>
-      <c r="G65" s="42"/>
-      <c r="H65" s="43"/>
-    </row>
-    <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="44" t="s">
+      <c r="B64" s="37"/>
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="37"/>
+      <c r="H64" s="38"/>
+    </row>
+    <row r="65" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="39"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="40"/>
+      <c r="D65" s="40"/>
+      <c r="E65" s="40"/>
+      <c r="F65" s="40"/>
+      <c r="G65" s="40"/>
+      <c r="H65" s="41"/>
+    </row>
+    <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="B66" s="39"/>
-      <c r="C66" s="39"/>
-      <c r="D66" s="39"/>
-      <c r="E66" s="39"/>
-      <c r="F66" s="39"/>
-      <c r="G66" s="39"/>
-      <c r="H66" s="40"/>
-    </row>
-    <row r="67" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="38" t="s">
+      <c r="B66" s="37"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="37"/>
+      <c r="F66" s="37"/>
+      <c r="G66" s="37"/>
+      <c r="H66" s="38"/>
+    </row>
+    <row r="67" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="B67" s="39"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="39"/>
-      <c r="E67" s="39"/>
-      <c r="F67" s="39"/>
-      <c r="G67" s="39"/>
-      <c r="H67" s="40"/>
-    </row>
-    <row r="68" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="41"/>
-      <c r="B68" s="42"/>
-      <c r="C68" s="42"/>
-      <c r="D68" s="42"/>
-      <c r="E68" s="42"/>
-      <c r="F68" s="42"/>
-      <c r="G68" s="42"/>
-      <c r="H68" s="43"/>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="46" t="s">
+      <c r="B67" s="37"/>
+      <c r="C67" s="37"/>
+      <c r="D67" s="37"/>
+      <c r="E67" s="37"/>
+      <c r="F67" s="37"/>
+      <c r="G67" s="37"/>
+      <c r="H67" s="38"/>
+    </row>
+    <row r="68" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="39"/>
+      <c r="B68" s="40"/>
+      <c r="C68" s="40"/>
+      <c r="D68" s="40"/>
+      <c r="E68" s="40"/>
+      <c r="F68" s="40"/>
+      <c r="G68" s="40"/>
+      <c r="H68" s="41"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="47"/>
-      <c r="C69" s="47"/>
-      <c r="D69" s="47"/>
-      <c r="E69" s="47"/>
-      <c r="F69" s="47"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="48"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="11"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="9"/>
     </row>
     <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="49" t="s">
+      <c r="A70" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="B70" s="50"/>
-      <c r="C70" s="50"/>
-      <c r="D70" s="50"/>
-      <c r="E70" s="50"/>
-      <c r="F70" s="50"/>
-      <c r="G70" s="50"/>
-      <c r="H70" s="51"/>
+      <c r="B70" s="46"/>
+      <c r="C70" s="46"/>
+      <c r="D70" s="46"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="46"/>
+      <c r="G70" s="46"/>
+      <c r="H70" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="68">

--- a/public/quote_template.xlsx
+++ b/public/quote_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C07DDE-038E-44A9-A349-1145657E3A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF4A846-49FA-494B-AAF4-81F8FA27D678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34230" yWindow="5265" windowWidth="28800" windowHeight="15315" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="문자광고_견적서" sheetId="1" r:id="rId1"/>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -116,9 +114,6 @@
     <t>지역①</t>
   </si>
   <si>
-    <t>지역③</t>
-  </si>
-  <si>
     <t>지역②</t>
   </si>
   <si>
@@ -322,6 +317,10 @@
   </si>
   <si>
     <t>② 다만 "을"이 기존에 보유하고 있던 저작물, 범용적으로 사용하는 템플릿 및 발송 시스템 등은 그러하지 아니하며, "을"에게 귀속된다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지역③</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -713,6 +712,39 @@
   <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -721,107 +753,74 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="12" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="14" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1142,923 +1141,975 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J70"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7265625" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="14.1796875" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" customWidth="1"/>
-    <col min="8" max="8" width="9.7265625" customWidth="1"/>
+    <col min="6" max="6" width="14.140625" customWidth="1"/>
+    <col min="7" max="7" width="20.28515625" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="2" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="8" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="17"/>
+    </row>
+    <row r="2" spans="1:10" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="20"/>
+    </row>
+    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10" t="s">
+      <c r="B3" s="26"/>
+      <c r="C3" s="31" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="26"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="24"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="24"/>
+      <c r="H4" s="26"/>
+    </row>
+    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="38"/>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="9"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="D5" s="25"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="39"/>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="24"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="26"/>
+    </row>
+    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="13" t="s">
+      <c r="C7" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="9"/>
-    </row>
-    <row r="5" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="15"/>
-      <c r="B5" s="13" t="s">
+      <c r="G7" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="26"/>
+    </row>
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="38"/>
+      <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="11"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="13" t="s">
+      <c r="C8" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17" t="s">
+      <c r="G8" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="18"/>
-      <c r="B6" s="13" t="s">
+      <c r="H8" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="38"/>
+      <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="13" t="s">
+      <c r="C9" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H6" s="9"/>
-    </row>
-    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="9"/>
-    </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="15"/>
-      <c r="B8" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="15"/>
-      <c r="B9" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="14" t="s">
+      <c r="G9" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="9"/>
-    </row>
-    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="18"/>
-      <c r="B10" s="13" t="s">
+      <c r="H9" s="26"/>
+    </row>
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="39"/>
+      <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="13" t="s">
+      <c r="D10" s="25"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="41">
         <v>46121</v>
       </c>
-      <c r="H10" s="9"/>
-    </row>
-    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="22" t="s">
+      <c r="H10" s="26"/>
+    </row>
+    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="22" t="s">
+      <c r="C11" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="22" t="str">
+      <c r="E11" s="6" t="str">
         <f>IF(OR(B12="호갱노노_단지마커",B12="직방_단지마커",B12="프리미엄_비즈마커"),"기간(일)","발송수량")</f>
         <v>발송수량</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="H11" s="9"/>
+      <c r="G11" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="26"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="24">
+    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
         <v>1</v>
       </c>
-      <c r="B12" s="24" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="D12" s="25" t="s">
+      <c r="B12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="9">
         <v>100000</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="9">
         <v>100</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="46">
         <f>IF(OR(F12="",E12=""),0,E12*F12)</f>
         <v>10000000</v>
       </c>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="28" t="s">
+      <c r="H12" s="26"/>
+    </row>
+    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="26"/>
+      <c r="E13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="26"/>
+    </row>
+    <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="38"/>
+      <c r="B14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="26"/>
+    </row>
+    <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="38"/>
+      <c r="B15" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="26"/>
+    </row>
+    <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="39"/>
+      <c r="B16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13" s="11"/>
-      <c r="H13" s="9"/>
-    </row>
-    <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14" s="15"/>
-      <c r="B14" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="9"/>
-    </row>
-    <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="15"/>
-      <c r="B15" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="9"/>
-    </row>
-    <row r="16" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" s="18"/>
-      <c r="B16" s="29" t="s">
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="26"/>
+    </row>
+    <row r="17" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="9"/>
-    </row>
-    <row r="17" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17" s="30" t="s">
+      <c r="B17" s="26"/>
+      <c r="C17" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="31" t="s">
+      <c r="D17" s="25"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="G17" s="33">
+      <c r="G17" s="45">
         <f>G12*1.1</f>
         <v>11000000</v>
       </c>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="34" t="s">
+      <c r="H17" s="26"/>
+    </row>
+    <row r="18" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="26"/>
+    </row>
+    <row r="19" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="9"/>
-    </row>
-    <row r="19" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="35" t="s">
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
-    </row>
-    <row r="20" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="36" t="s">
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="23"/>
+    </row>
+    <row r="21" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="38"/>
-    </row>
-    <row r="21" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="36" t="s">
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="23"/>
+    </row>
+    <row r="22" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="38"/>
-    </row>
-    <row r="22" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="36" t="s">
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="23"/>
+    </row>
+    <row r="23" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="14"/>
+    </row>
+    <row r="24" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="38"/>
-    </row>
-    <row r="23" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="39"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="41"/>
-    </row>
-    <row r="24" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="42" t="s">
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="23"/>
+    </row>
+    <row r="25" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="23"/>
+    </row>
+    <row r="26" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="12"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="14"/>
+    </row>
+    <row r="27" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="38"/>
-    </row>
-    <row r="25" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="36" t="s">
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="23"/>
+    </row>
+    <row r="28" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="38"/>
-    </row>
-    <row r="26" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="39"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="41"/>
-    </row>
-    <row r="27" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="42" t="s">
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="23"/>
+    </row>
+    <row r="29" spans="1:8" ht="3" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="B27" s="37"/>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="38"/>
-    </row>
-    <row r="28" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="36" t="s">
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="23"/>
+    </row>
+    <row r="30" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="12"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="14"/>
+    </row>
+    <row r="31" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="23"/>
+    </row>
+    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="37"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="38"/>
-    </row>
-    <row r="29" spans="1:8" ht="3" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="43" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="37"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="37"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="37"/>
-      <c r="H29" s="38"/>
-    </row>
-    <row r="30" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="39"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="41"/>
-    </row>
-    <row r="31" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="42" t="s">
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="23"/>
+    </row>
+    <row r="33" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="23"/>
+    </row>
+    <row r="34" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="14"/>
+    </row>
+    <row r="35" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="37"/>
-      <c r="C31" s="37"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="37"/>
-      <c r="F31" s="37"/>
-      <c r="G31" s="37"/>
-      <c r="H31" s="38"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="36" t="s">
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="23"/>
+    </row>
+    <row r="36" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="23"/>
+    </row>
+    <row r="37" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="23"/>
+    </row>
+    <row r="38" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="23"/>
+    </row>
+    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="23"/>
+    </row>
+    <row r="40" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="14"/>
+    </row>
+    <row r="41" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="23"/>
+    </row>
+    <row r="42" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="23"/>
+    </row>
+    <row r="43" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="12"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="14"/>
+    </row>
+    <row r="44" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="23"/>
+    </row>
+    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="23"/>
+    </row>
+    <row r="46" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="12"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
+      <c r="H46" s="14"/>
+    </row>
+    <row r="47" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="22"/>
+      <c r="H47" s="23"/>
+    </row>
+    <row r="48" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="B32" s="37"/>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="37"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="38"/>
-    </row>
-    <row r="33" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="B33" s="37"/>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
-      <c r="G33" s="37"/>
-      <c r="H33" s="38"/>
-    </row>
-    <row r="34" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="39"/>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
-      <c r="E34" s="40"/>
-      <c r="F34" s="40"/>
-      <c r="G34" s="40"/>
-      <c r="H34" s="41"/>
-    </row>
-    <row r="35" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" s="42" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="37"/>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="38"/>
-    </row>
-    <row r="36" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="37"/>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="38"/>
-    </row>
-    <row r="37" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37" s="36" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="38"/>
-    </row>
-    <row r="38" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37"/>
-      <c r="G38" s="37"/>
-      <c r="H38" s="38"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="37"/>
-      <c r="C39" s="37"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="38"/>
-    </row>
-    <row r="40" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="39"/>
-      <c r="B40" s="40"/>
-      <c r="C40" s="40"/>
-      <c r="D40" s="40"/>
-      <c r="E40" s="40"/>
-      <c r="F40" s="40"/>
-      <c r="G40" s="40"/>
-      <c r="H40" s="41"/>
-    </row>
-    <row r="41" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41" s="37"/>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="38"/>
-    </row>
-    <row r="42" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="36" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="37"/>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="38"/>
-    </row>
-    <row r="43" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="39"/>
-      <c r="B43" s="40"/>
-      <c r="C43" s="40"/>
-      <c r="D43" s="40"/>
-      <c r="E43" s="40"/>
-      <c r="F43" s="40"/>
-      <c r="G43" s="40"/>
-      <c r="H43" s="41"/>
-    </row>
-    <row r="44" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="B44" s="37"/>
-      <c r="C44" s="37"/>
-      <c r="D44" s="37"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="38"/>
-    </row>
-    <row r="45" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="B45" s="37"/>
-      <c r="C45" s="37"/>
-      <c r="D45" s="37"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="38"/>
-    </row>
-    <row r="46" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="39"/>
-      <c r="B46" s="40"/>
-      <c r="C46" s="40"/>
-      <c r="D46" s="40"/>
-      <c r="E46" s="40"/>
-      <c r="F46" s="40"/>
-      <c r="G46" s="40"/>
-      <c r="H46" s="41"/>
-    </row>
-    <row r="47" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="42" t="s">
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="22"/>
+      <c r="H48" s="23"/>
+    </row>
+    <row r="49" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="22"/>
+      <c r="H49" s="23"/>
+    </row>
+    <row r="50" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="12"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="14"/>
+    </row>
+    <row r="51" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="B47" s="37"/>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="38"/>
-    </row>
-    <row r="48" spans="1:8" ht="11.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="B48" s="37"/>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="38"/>
-    </row>
-    <row r="49" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="36" t="s">
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="22"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="22"/>
+      <c r="H51" s="23"/>
+    </row>
+    <row r="52" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="B49" s="37"/>
-      <c r="C49" s="37"/>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37"/>
-      <c r="H49" s="38"/>
-    </row>
-    <row r="50" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="39"/>
-      <c r="B50" s="40"/>
-      <c r="C50" s="40"/>
-      <c r="D50" s="40"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="40"/>
-      <c r="H50" s="41"/>
-    </row>
-    <row r="51" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="42" t="s">
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="23"/>
+    </row>
+    <row r="53" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="22"/>
+      <c r="H53" s="23"/>
+    </row>
+    <row r="54" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="12"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="14"/>
+    </row>
+    <row r="55" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B51" s="37"/>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="38"/>
-    </row>
-    <row r="52" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="B52" s="37"/>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="38"/>
-    </row>
-    <row r="53" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="B53" s="37"/>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="37"/>
-      <c r="H53" s="38"/>
-    </row>
-    <row r="54" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="39"/>
-      <c r="B54" s="40"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="40"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="41"/>
-    </row>
-    <row r="55" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="42" t="s">
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="23"/>
+    </row>
+    <row r="56" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="B55" s="37"/>
-      <c r="C55" s="37"/>
-      <c r="D55" s="37"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="37"/>
-      <c r="H55" s="38"/>
-    </row>
-    <row r="56" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="36" t="s">
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="22"/>
+      <c r="H56" s="23"/>
+    </row>
+    <row r="57" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="12"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="14"/>
+    </row>
+    <row r="58" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B56" s="37"/>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="38"/>
-    </row>
-    <row r="57" spans="1:8" ht="0.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="39"/>
-      <c r="B57" s="40"/>
-      <c r="C57" s="40"/>
-      <c r="D57" s="40"/>
-      <c r="E57" s="40"/>
-      <c r="F57" s="40"/>
-      <c r="G57" s="40"/>
-      <c r="H57" s="41"/>
-    </row>
-    <row r="58" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="42" t="s">
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="23"/>
+    </row>
+    <row r="59" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="37"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="38"/>
-    </row>
-    <row r="59" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="36" t="s">
+      <c r="B59" s="22"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="22"/>
+      <c r="H59" s="23"/>
+    </row>
+    <row r="60" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="12"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="14"/>
+    </row>
+    <row r="61" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B59" s="37"/>
-      <c r="C59" s="37"/>
-      <c r="D59" s="37"/>
-      <c r="E59" s="37"/>
-      <c r="F59" s="37"/>
-      <c r="G59" s="37"/>
-      <c r="H59" s="38"/>
-    </row>
-    <row r="60" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="39"/>
-      <c r="B60" s="40"/>
-      <c r="C60" s="40"/>
-      <c r="D60" s="40"/>
-      <c r="E60" s="40"/>
-      <c r="F60" s="40"/>
-      <c r="G60" s="40"/>
-      <c r="H60" s="41"/>
-    </row>
-    <row r="61" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="42" t="s">
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="23"/>
+    </row>
+    <row r="62" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="B61" s="37"/>
-      <c r="C61" s="37"/>
-      <c r="D61" s="37"/>
-      <c r="E61" s="37"/>
-      <c r="F61" s="37"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="38"/>
-    </row>
-    <row r="62" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" s="36" t="s">
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="23"/>
+    </row>
+    <row r="63" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="B62" s="37"/>
-      <c r="C62" s="37"/>
-      <c r="D62" s="37"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="37"/>
-      <c r="G62" s="37"/>
-      <c r="H62" s="38"/>
-    </row>
-    <row r="63" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" s="36" t="s">
+      <c r="B63" s="22"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="23"/>
+    </row>
+    <row r="64" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="B63" s="37"/>
-      <c r="C63" s="37"/>
-      <c r="D63" s="37"/>
-      <c r="E63" s="37"/>
-      <c r="F63" s="37"/>
-      <c r="G63" s="37"/>
-      <c r="H63" s="38"/>
-    </row>
-    <row r="64" spans="1:8" ht="10.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A64" s="36" t="s">
+      <c r="B64" s="22"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="22"/>
+      <c r="H64" s="23"/>
+    </row>
+    <row r="65" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="12"/>
+      <c r="B65" s="13"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="14"/>
+    </row>
+    <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B64" s="37"/>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
-      <c r="F64" s="37"/>
-      <c r="G64" s="37"/>
-      <c r="H64" s="38"/>
-    </row>
-    <row r="65" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A65" s="39"/>
-      <c r="B65" s="40"/>
-      <c r="C65" s="40"/>
-      <c r="D65" s="40"/>
-      <c r="E65" s="40"/>
-      <c r="F65" s="40"/>
-      <c r="G65" s="40"/>
-      <c r="H65" s="41"/>
-    </row>
-    <row r="66" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A66" s="42" t="s">
+      <c r="B66" s="22"/>
+      <c r="C66" s="22"/>
+      <c r="D66" s="22"/>
+      <c r="E66" s="22"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="23"/>
+    </row>
+    <row r="67" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B66" s="37"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="37"/>
-      <c r="F66" s="37"/>
-      <c r="G66" s="37"/>
-      <c r="H66" s="38"/>
-    </row>
-    <row r="67" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A67" s="36" t="s">
+      <c r="B67" s="22"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="23"/>
+    </row>
+    <row r="68" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="12"/>
+      <c r="B68" s="13"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="13"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="14"/>
+    </row>
+    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="B67" s="37"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="37"/>
-      <c r="F67" s="37"/>
-      <c r="G67" s="37"/>
-      <c r="H67" s="38"/>
-    </row>
-    <row r="68" spans="1:8" ht="1.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A68" s="39"/>
-      <c r="B68" s="40"/>
-      <c r="C68" s="40"/>
-      <c r="D68" s="40"/>
-      <c r="E68" s="40"/>
-      <c r="F68" s="40"/>
-      <c r="G68" s="40"/>
-      <c r="H68" s="41"/>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" s="44" t="s">
+      <c r="B69" s="25"/>
+      <c r="C69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="25"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="25"/>
+      <c r="H69" s="26"/>
+    </row>
+    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="11"/>
-      <c r="C69" s="11"/>
-      <c r="D69" s="11"/>
-      <c r="E69" s="11"/>
-      <c r="F69" s="11"/>
-      <c r="G69" s="11"/>
-      <c r="H69" s="9"/>
-    </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="45" t="s">
-        <v>60</v>
-      </c>
-      <c r="B70" s="46"/>
-      <c r="C70" s="46"/>
-      <c r="D70" s="46"/>
-      <c r="E70" s="46"/>
-      <c r="F70" s="46"/>
-      <c r="G70" s="46"/>
-      <c r="H70" s="47"/>
+      <c r="B70" s="33"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="33"/>
+      <c r="F70" s="33"/>
+      <c r="G70" s="33"/>
+      <c r="H70" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="68">
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A29:H29"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="A63:H63"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="C6:E6"/>
@@ -2075,58 +2126,6 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="A70:H70"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A7:A10"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A63:H63"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="1">
